--- a/assets/BASE DE DATOS.xlsx
+++ b/assets/BASE DE DATOS.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Danielito\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{162D9AF6-3688-442A-A543-C02D4B1BEAA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{106DF3D3-F7FE-49E9-B365-40573068DC7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4645DC94-C64F-4465-B5F5-5363EF951AA2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{4645DC94-C64F-4465-B5F5-5363EF951AA2}"/>
   </bookViews>
   <sheets>
-    <sheet name="FUNDACIONES" sheetId="1" r:id="rId1"/>
+    <sheet name="FUNDACION" sheetId="1" r:id="rId1"/>
     <sheet name="ITEMS" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
